--- a/Module Pinouts.xlsx
+++ b/Module Pinouts.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Arduino\canbus2cluster\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\PlatformIO\Can2Cluster\PlatformIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B7E02E-4DA4-45CB-88F6-8061F60514DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4223AB5-ACC3-4724-A052-BDA9BA3EE62E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2277D2B6-EF2D-4C47-8FFA-EE2E6ABE4DEA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{2277D2B6-EF2D-4C47-8FFA-EE2E6ABE4DEA}"/>
   </bookViews>
   <sheets>
     <sheet name="V1" sheetId="1" r:id="rId1"/>
     <sheet name="V2" sheetId="2" r:id="rId2"/>
+    <sheet name="Mini" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="43">
   <si>
     <t>Pin Number</t>
   </si>
@@ -143,6 +144,18 @@
   </si>
   <si>
     <t>High voltage coil pulse - for MK1/MK2 etc</t>
+  </si>
+  <si>
+    <t>12v - pull-to-ground pulsed speed output</t>
+  </si>
+  <si>
+    <t>12v - pull-to-ground pulsed RPM output</t>
+  </si>
+  <si>
+    <t>12v - pull-to-ground Engine Management Light</t>
+  </si>
+  <si>
+    <t>12v - pull-to-ground Electronic Pedal Control Light</t>
   </si>
 </sst>
 </file>
@@ -166,7 +179,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,6 +225,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -394,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -437,6 +468,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,6 +625,116 @@
         <a:xfrm>
           <a:off x="676275" y="4048125"/>
           <a:ext cx="5534797" cy="4629796"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4000500</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2110588</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DF739B1-FE2A-481E-89B0-B5588134440B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6629400" y="3825240"/>
+          <a:ext cx="4564228" cy="3676650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>160707</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>3919926</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>88329</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31A80400-1AE0-6449-C324-03CD5F2D6C9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="723900" y="2743887"/>
+          <a:ext cx="5824926" cy="3036582"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -894,15 +1044,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93B0216-9375-4A53-8F13-64B98558BF00}">
   <dimension ref="B2:D20"/>
-  <sheetFormatPr defaultColWidth="37.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="37.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="94.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="94.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -913,7 +1063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="4">
         <v>1</v>
       </c>
@@ -924,7 +1074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="10">
         <v>2</v>
       </c>
@@ -935,7 +1085,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="7">
         <v>3</v>
       </c>
@@ -946,7 +1096,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="7">
         <v>4</v>
       </c>
@@ -957,7 +1107,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="19">
         <v>5</v>
       </c>
@@ -968,7 +1118,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="7">
         <v>6</v>
       </c>
@@ -979,7 +1129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="19">
         <v>7</v>
       </c>
@@ -990,7 +1140,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="10">
         <v>8</v>
       </c>
@@ -1001,7 +1151,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" s="7">
         <v>9</v>
       </c>
@@ -1012,7 +1162,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" s="10">
         <v>10</v>
       </c>
@@ -1023,7 +1173,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="7">
         <v>11</v>
       </c>
@@ -1034,7 +1184,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="13">
         <v>12</v>
       </c>
@@ -1045,7 +1195,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="7">
         <v>13</v>
       </c>
@@ -1056,7 +1206,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="13">
         <v>14</v>
       </c>
@@ -1067,7 +1217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="7">
         <v>15</v>
       </c>
@@ -1078,7 +1228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="13">
         <v>16</v>
       </c>
@@ -1089,7 +1239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="13">
         <v>17</v>
       </c>
@@ -1100,7 +1250,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B20" s="16">
         <v>18</v>
       </c>
@@ -1121,16 +1271,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E690C91C-13A2-49BD-A55E-F599A007AB2B}">
   <dimension ref="B1:D20"/>
-  <sheetFormatPr defaultColWidth="37.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="37.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="94.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="94.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
@@ -1141,7 +1291,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B3" s="24">
         <v>1</v>
       </c>
@@ -1152,7 +1302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B4" s="26">
         <v>2</v>
       </c>
@@ -1163,7 +1313,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B5" s="28">
         <v>3</v>
       </c>
@@ -1174,7 +1324,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B6" s="28">
         <v>4</v>
       </c>
@@ -1185,7 +1335,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B7" s="30">
         <v>5</v>
       </c>
@@ -1196,7 +1346,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B8" s="30">
         <v>6</v>
       </c>
@@ -1207,7 +1357,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B9" s="30">
         <v>7</v>
       </c>
@@ -1218,7 +1368,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B10" s="30">
         <v>8</v>
       </c>
@@ -1229,7 +1379,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B11" s="32">
         <v>9</v>
       </c>
@@ -1240,7 +1390,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B12" s="34">
         <v>10</v>
       </c>
@@ -1251,7 +1401,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B13" s="34">
         <v>11</v>
       </c>
@@ -1262,7 +1412,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B14" s="34">
         <v>12</v>
       </c>
@@ -1273,7 +1423,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B15" s="32">
         <v>13</v>
       </c>
@@ -1284,7 +1434,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B16" s="32">
         <v>14</v>
       </c>
@@ -1295,7 +1445,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="32">
         <v>15</v>
       </c>
@@ -1306,7 +1456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="32">
         <v>16</v>
       </c>
@@ -1317,7 +1467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B19" s="32">
         <v>17</v>
       </c>
@@ -1328,7 +1478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="36">
         <v>18</v>
       </c>
@@ -1337,6 +1487,168 @@
       </c>
       <c r="D20" s="38" t="s">
         <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F51AEAF1-D83E-46E1-BDCB-0D295DD67499}">
+  <dimension ref="B1:D14"/>
+  <sheetFormatPr defaultColWidth="37.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="94.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="24">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="26">
+        <v>2</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="28">
+        <v>3</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="28">
+        <v>4</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="34">
+        <v>5</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="34">
+        <v>6</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="30">
+        <v>7</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="30">
+        <v>8</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="42">
+        <v>9</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" s="42">
+        <v>10</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="45">
+        <v>11</v>
+      </c>
+      <c r="C13" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="48">
+        <v>12</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
